--- a/Output/ModelAggregates/PrimaryModels.xlsx
+++ b/Output/ModelAggregates/PrimaryModels.xlsx
@@ -1178,10 +1178,10 @@
         <v>50.096</v>
       </c>
       <c r="G18">
-        <v>26.209</v>
+        <v>26.695</v>
       </c>
       <c r="H18">
-        <v>33.649</v>
+        <v>33.162</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>47.054</v>
       </c>
       <c r="G19">
-        <v>-2.973</v>
+        <v>-2.767</v>
       </c>
       <c r="H19">
-        <v>0.166</v>
+        <v>-0.04</v>
       </c>
       <c r="I19">
         <v>0.044</v>
@@ -1270,10 +1270,10 @@
         <v>46.672</v>
       </c>
       <c r="G20">
-        <v>-3.405</v>
+        <v>-3.107</v>
       </c>
       <c r="H20">
-        <v>1.142</v>
+        <v>0.844</v>
       </c>
       <c r="I20">
         <v>0.255</v>
@@ -1316,10 +1316,10 @@
         <v>49.274</v>
       </c>
       <c r="G21">
-        <v>-2.157</v>
+        <v>-1.397</v>
       </c>
       <c r="H21">
-        <v>9.456</v>
+        <v>8.696</v>
       </c>
       <c r="I21">
         <v>0.153</v>
@@ -1362,10 +1362,10 @@
         <v>49.263</v>
       </c>
       <c r="G22">
-        <v>-1.874</v>
+        <v>-1.727</v>
       </c>
       <c r="H22">
-        <v>0.367</v>
+        <v>0.221</v>
       </c>
       <c r="I22">
         <v>0.127</v>
@@ -1408,10 +1408,10 @@
         <v>41.768</v>
       </c>
       <c r="G23">
-        <v>0.514</v>
+        <v>0.885</v>
       </c>
       <c r="H23">
-        <v>6.137</v>
+        <v>5.766</v>
       </c>
       <c r="I23">
         <v>0.008999999999999999</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="K23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>0.018</v>
@@ -1454,10 +1454,10 @@
         <v>47.341</v>
       </c>
       <c r="G24">
-        <v>-0.578</v>
+        <v>-0.513</v>
       </c>
       <c r="H24">
-        <v>0.402</v>
+        <v>0.337</v>
       </c>
       <c r="I24">
         <v>0.679</v>
@@ -1500,10 +1500,10 @@
         <v>46.146</v>
       </c>
       <c r="G25">
-        <v>-0.5659999999999999</v>
+        <v>-0.478</v>
       </c>
       <c r="H25">
-        <v>0.776</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="I25">
         <v>0.718</v>
@@ -1546,10 +1546,10 @@
         <v>40.761</v>
       </c>
       <c r="G26">
-        <v>-1.492</v>
+        <v>-1.368</v>
       </c>
       <c r="H26">
-        <v>0.384</v>
+        <v>0.261</v>
       </c>
       <c r="I26">
         <v>0.177</v>
